--- a/docs/Rubrics_AgenticAI.xlsx
+++ b/docs/Rubrics_AgenticAI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nimrita Koul\Documents\3Teaching2022Onwards\Teaching2026_FebtoJune\AgenticAI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nimrita Koul\Documents\3Teaching2022Onwards\Teaching2026_FebtoJune\AgenticAI\AgenticAI_CourseProjects2026\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03A92703-D189-407F-A753-6BB1EF62621F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDCEA65-8D36-46F3-A470-26506AC02D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
